--- a/apps/web/lib/notebooks/fixtures/xlsx/number-formats.xlsx
+++ b/apps/web/lib/notebooks/fixtures/xlsx/number-formats.xlsx
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0&quot; widgets&quot;"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,11 +51,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +481,36 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>grouped number</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1234567.891</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>builtin percent</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>a format we will not render</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
